--- a/Data/Rules/Dexy Paws Rules Matrix.xlsx
+++ b/Data/Rules/Dexy Paws Rules Matrix.xlsx
@@ -808,10 +808,10 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -930,10 +930,10 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -1296,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -1540,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         <v>2</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>2</v>
       </c>
       <c r="AE9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="b">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>2</v>
       </c>
       <c r="S10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         <v>2</v>
       </c>
       <c r="AE10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF10" t="b">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>2</v>
       </c>
       <c r="S11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>2</v>
       </c>
       <c r="AE11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="b">
         <v>0</v>
@@ -2031,7 +2031,7 @@
         <v>2</v>
       </c>
       <c r="S12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
@@ -2067,7 +2067,7 @@
         <v>2</v>
       </c>
       <c r="AE12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="b">
         <v>0</v>
@@ -2153,7 +2153,7 @@
         <v>2</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T13" t="b">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>2</v>
       </c>
       <c r="AE13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF13" t="b">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>2</v>
       </c>
       <c r="S14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>2</v>
       </c>
       <c r="AE14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="b">
         <v>0</v>
@@ -2397,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="S15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
@@ -2433,7 +2433,7 @@
         <v>2</v>
       </c>
       <c r="AE15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF15" t="b">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>2</v>
       </c>
       <c r="S16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="b">
         <v>0</v>
@@ -2555,7 +2555,7 @@
         <v>2</v>
       </c>
       <c r="AE16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="b">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>2</v>
       </c>
       <c r="S17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" t="b">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="AE17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="b">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>2</v>
       </c>
       <c r="S18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T18" t="b">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>2</v>
       </c>
       <c r="AE18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF18" t="b">
         <v>0</v>
@@ -2885,7 +2885,7 @@
         <v>2</v>
       </c>
       <c r="S19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T19" t="b">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>2</v>
       </c>
       <c r="AE19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF19" t="b">
         <v>0</v>
@@ -3007,7 +3007,7 @@
         <v>2</v>
       </c>
       <c r="S20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T20" t="b">
         <v>0</v>
@@ -3043,7 +3043,7 @@
         <v>2</v>
       </c>
       <c r="AE20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF20" t="b">
         <v>0</v>
@@ -3129,7 +3129,7 @@
         <v>2</v>
       </c>
       <c r="S21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="b">
         <v>0</v>
@@ -3165,7 +3165,7 @@
         <v>2</v>
       </c>
       <c r="AE21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF21" t="b">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>2</v>
       </c>
       <c r="S22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T22" t="b">
         <v>0</v>
@@ -3287,7 +3287,7 @@
         <v>2</v>
       </c>
       <c r="AE22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="b">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         <v>2</v>
       </c>
       <c r="S23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T23" t="b">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>2</v>
       </c>
       <c r="AE23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF23" t="b">
         <v>0</v>
@@ -3495,7 +3495,7 @@
         <v>2</v>
       </c>
       <c r="S24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" t="b">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>2</v>
       </c>
       <c r="AE24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF24" t="b">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>2</v>
       </c>
       <c r="S25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="b">
         <v>0</v>
@@ -3653,7 +3653,7 @@
         <v>2</v>
       </c>
       <c r="AE25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF25" t="b">
         <v>0</v>
@@ -3739,7 +3739,7 @@
         <v>2</v>
       </c>
       <c r="S26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="b">
         <v>0</v>
@@ -3775,7 +3775,7 @@
         <v>2</v>
       </c>
       <c r="AE26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF26" t="b">
         <v>0</v>
@@ -3861,7 +3861,7 @@
         <v>2</v>
       </c>
       <c r="S27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T27" t="b">
         <v>0</v>
@@ -3897,7 +3897,7 @@
         <v>2</v>
       </c>
       <c r="AE27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF27" t="b">
         <v>0</v>
@@ -3983,7 +3983,7 @@
         <v>2</v>
       </c>
       <c r="S28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="b">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>2</v>
       </c>
       <c r="AE28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF28" t="b">
         <v>0</v>
